--- a/data/trans_orig/IP1006-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1006-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48467</t>
+          <t>48796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108536</t>
+          <t>108333</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98248</t>
+          <t>97982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206987</t>
+          <t>206574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41825</t>
+          <t>41271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83090</t>
+          <t>82571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154323</t>
+          <t>154368</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>159223</t>
+          <t>159662</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>316526</t>
+          <t>316544</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>321320</t>
+          <t>321323</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>675075</t>
+          <t>675346</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>680360</t>
+          <t>680379</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>716410</t>
+          <t>717154</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>722016</t>
+          <t>722015</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1394046</t>
+          <t>1394312</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1401790</t>
+          <t>1401662</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54049</t>
+          <t>54173</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60168</t>
+          <t>60158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>107095</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113142</t>
+          <t>113138</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67200</t>
+          <t>67223</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135711</t>
+          <t>135367</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77221</t>
+          <t>78191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156033</t>
+          <t>155733</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42403</t>
+          <t>42111</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86731</t>
+          <t>86776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56718</t>
+          <t>56734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112779</t>
+          <t>112754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134462</t>
+          <t>135274</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>280391</t>
+          <t>281384</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161397</t>
+          <t>160989</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167837</t>
+          <t>167904</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>330940</t>
+          <t>331341</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11337</t>
+          <t>11705</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>702839</t>
+          <t>702219</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>736805</t>
+          <t>736437</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>745464</t>
+          <t>745402</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1441692</t>
+          <t>1442035</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1451294</t>
+          <t>1451500</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107101</t>
+          <t>106484</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211090</t>
+          <t>211044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66153</t>
+          <t>65950</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132251</t>
+          <t>132599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72669</t>
+          <t>72251</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153622</t>
+          <t>153224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39863</t>
+          <t>40166</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86025</t>
+          <t>86281</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134527</t>
+          <t>134339</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>278450</t>
+          <t>277783</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161565</t>
+          <t>161472</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167707</t>
+          <t>167706</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331230</t>
+          <t>331337</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>698133</t>
+          <t>697614</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>703767</t>
+          <t>703713</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>739583</t>
+          <t>739353</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>744220</t>
+          <t>744218</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1439745</t>
+          <t>1439610</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1447277</t>
+          <t>1447214</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1006-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1006-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1207</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3772</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4213</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4178</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1207</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4452</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>51361</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48796</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48355</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,7%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>91,99%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>168</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108333</t>
+          <t>108607</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3580</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3585</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3745</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>100901</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>97982</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>98250</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>319</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206574</t>
+          <t>206734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1864,47 +1864,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>720</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3572</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4434</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4124</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44123</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>41234</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44123</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>41271</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82571</t>
+          <t>82261</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2893,47 +2893,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3123,107 +3123,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4178</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3536</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3598</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1380</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4396</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>5360</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>5418</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -3236,107 +3236,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>162678</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>159880</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,45%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>157262</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>154368</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>154306</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,59%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>162678</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>159662</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>319940</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>316602</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>321962</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>319940</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>316544</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>321323</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5639</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>2510</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5675</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>6411</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5546</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -3579,72 +3579,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>720600</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>717061</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>722016</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1014</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>678511</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>675346</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>680379</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>674610</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>680356</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>720600</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>717154</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>722015</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1394312</t>
+          <t>1394117</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1401662</t>
+          <t>1401706</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4045,92 +4045,92 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2406</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6588</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2406</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>591</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -4158,72 +4158,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>58355</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>53976</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>60177</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>58355</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>54173</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>60158</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,04%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107095</t>
+          <t>106327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113138</t>
+          <t>113134</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4501,47 +4501,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4731,107 +4731,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>670</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>670</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3361</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3191</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3395</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -4844,72 +4844,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69914</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67252</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,28%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69914</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>67223</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135367</t>
+          <t>135571</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5074,107 +5074,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>793</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>793</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4043</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3253</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4262</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -5187,72 +5187,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81441</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78581</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81441</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>78191</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155733</t>
+          <t>156742</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5417,107 +5417,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>652</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>652</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3994</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3408</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3230</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -5530,72 +5530,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>45453</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>41884</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,84%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>45453</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>42111</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86776</t>
+          <t>86598</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5760,107 +5760,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>687</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3511</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3439</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3476</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -5873,72 +5873,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59558</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>56698</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59558</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>56734</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112754</t>
+          <t>112791</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6103,107 +6103,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>685</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3444</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3440</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3073</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -6216,74 +6216,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138033</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>135274</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>135288</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,51%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,53%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>399</t>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>281384</t>
+          <t>281017</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6451,102 +6451,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3657</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3719</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3758</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3411</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4361</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1340</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4682</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -6559,102 +6559,102 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170636</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>167658</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164047</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>160989</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>160950</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,6%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170636</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>167904</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>334683</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>331662</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>336023</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t>99,6%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>334683</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>331341</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>336023</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6789,74 +6789,74 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>11602</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1346</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>4746</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2740</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>11705</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -6902,74 +6902,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>742253</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>736540</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>745641</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>705582</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>702219</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>702182</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>99,33%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>742253</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>736437</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>745402</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2074</t>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1442035</t>
+          <t>1442091</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1451500</t>
+          <t>1451219</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7481,47 +7481,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7711,107 +7711,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>634</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>634</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3799</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3094</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -7824,72 +7824,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>109649</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>106691</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>109649</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>106484</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211044</t>
+          <t>211136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8054,107 +8054,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>740</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3955</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3690</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4137</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -8167,72 +8167,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69165</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>66489</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69165</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>65950</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,94%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132599</t>
+          <t>133046</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8397,107 +8397,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>874</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4710</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4371</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4847</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4921</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -8510,74 +8510,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76087</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>72251</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>72590</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,86%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,32%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>218</t>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153224</t>
+          <t>153298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8740,107 +8740,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>662</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2954</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3507</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -8853,74 +8853,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>42776</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>40166</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>40484</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,48%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,47%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>93,2%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>130</t>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86281</t>
+          <t>86423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8966,57 +8966,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9426,107 +9426,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3035</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3449</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>2992</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3663</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -9539,74 +9539,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>136774</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>134339</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>133925</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,56%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>414</t>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>277783</t>
+          <t>278454</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9774,102 +9774,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4132</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2704</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2660</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3143</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1162</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4025</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1162</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3688</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -9882,74 +9882,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170223</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>166717</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>163640</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>161472</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>161516</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170223</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>167706</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>514</t>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331337</t>
+          <t>331000</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10112,72 +10112,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6071</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>2673</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>6757</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>6913</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5491</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -10225,74 +10225,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>742845</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>738773</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>744217</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1057</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>701698</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>697614</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>703713</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>697458</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>703769</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>742845</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>739353</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>744218</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2119</t>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1439610</t>
+          <t>1440063</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1447214</t>
+          <t>1447335</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
